--- a/Week_4/capabilities.xlsx
+++ b/Week_4/capabilities.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\EthanWilson\Git_Repos\SNOW\Week_4\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F35B4B84-84BE-4AD3-A749-0B13015BDE83}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AB2130AB-B7BA-4379-BF0E-345ACEFF2D02}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3855" yWindow="3855" windowWidth="19185" windowHeight="10065" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="5670" yWindow="5655" windowWidth="19185" windowHeight="10065" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,12 +36,6 @@
     <t xml:space="preserve"> Full-Stack</t>
   </si>
   <si>
-    <t xml:space="preserve"> Full-Stack </t>
-  </si>
-  <si>
-    <t xml:space="preserve"> COTS</t>
-  </si>
-  <si>
     <t>Full Stack with Java with Microservices</t>
   </si>
   <si>
@@ -52,6 +46,12 @@
   </si>
   <si>
     <t>Pega with React</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> C.O.T.S.</t>
+  </si>
+  <si>
+    <t>Full-Stack</t>
   </si>
 </sst>
 </file>
@@ -372,8 +372,8 @@
   <dimension ref="A1:B5"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="18.5703125" customWidth="1"/>
-    <col min="2" max="2" width="12.140625" customWidth="1"/>
+    <col min="1" max="1" width="33.28515625" customWidth="1"/>
+    <col min="2" max="2" width="24.140625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
@@ -386,7 +386,7 @@
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="B2" t="s">
         <v>2</v>
@@ -394,26 +394,26 @@
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="B3" t="s">
-        <v>3</v>
+        <v>8</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
+        <v>5</v>
+      </c>
+      <c r="B4" t="s">
         <v>7</v>
-      </c>
-      <c r="B4" t="s">
-        <v>4</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="B5" t="s">
-        <v>4</v>
+        <v>7</v>
       </c>
     </row>
   </sheetData>
